--- a/Ecom/Test_Data/Project_Data_Amazon.xlsx
+++ b/Ecom/Test_Data/Project_Data_Amazon.xlsx
@@ -8,26 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8EEFF3BC-FE10-497F-AD7C-36E846C6833C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76F5DBCA-71D2-400F-8EA8-117A2D40B9B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{67DF11A2-EBA1-4A69-BD1F-2E2B19CA27D7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
   <si>
     <t>Search_Product</t>
   </si>
   <si>
-    <t>Count</t>
-  </si>
-  <si>
     <t>Mobile</t>
   </si>
   <si>
@@ -41,6 +39,24 @@
   </si>
   <si>
     <t>Laptop bag</t>
+  </si>
+  <si>
+    <t>UserName</t>
+  </si>
+  <si>
+    <t>Password</t>
+  </si>
+  <si>
+    <t>9923655602</t>
+  </si>
+  <si>
+    <t>Abhi4816</t>
+  </si>
+  <si>
+    <t>kawankarsweety@gmail.com</t>
+  </si>
+  <si>
+    <t>Quantity</t>
   </si>
 </sst>
 </file>
@@ -75,8 +91,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" customBuiltin="1"/>
@@ -391,46 +413,82 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C923CBEA-274A-4FBD-AD60-AE45DAE4C300}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="20.21875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="3" max="3" width="13.88671875" customWidth="1"/>
+    <col min="4" max="4" width="8.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="28.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.70000000000000007" right="0.70000000000000007" top="0.75" bottom="0.75" header="0.30000000000000004" footer="0.30000000000000004"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDC3B6CD-0B7C-46FA-994E-E6A8BEDC4FF8}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="13.88671875" customWidth="1"/>
-    <col min="2" max="2" width="8.88671875" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
         <v>2</v>
-      </c>
-      <c r="B2" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" t="s">
         <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.70000000000000007" right="0.70000000000000007" top="0.75" bottom="0.75" header="0.30000000000000004" footer="0.30000000000000004"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>